--- a/llm_stats/token_usage.xlsx
+++ b/llm_stats/token_usage.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="PromptVersionSummary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ModelSummary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Legend" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,8 +417,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="59" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="66" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="12" max="12"/>
+    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="66" customWidth="1" min="18" max="18"/>
+    <col width="80" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="15" customWidth="1" min="31" max="31"/>
+    <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="28" customWidth="1" min="34" max="34"/>
+    <col width="22" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="36" max="36"/>
+    <col width="80" customWidth="1" min="37" max="37"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+    <col width="16" customWidth="1" min="42" max="42"/>
+    <col width="23" customWidth="1" min="43" max="43"/>
+    <col width="24" customWidth="1" min="44" max="44"/>
+    <col width="18" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="46" max="46"/>
+    <col width="22" customWidth="1" min="47" max="47"/>
+    <col width="24" customWidth="1" min="48" max="48"/>
+    <col width="24" customWidth="1" min="49" max="49"/>
+    <col width="17" customWidth="1" min="50" max="50"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -692,7 +745,11 @@
           <t>Find Users with High Token Usage</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>easy</t>
@@ -718,7 +775,21 @@
           <t>legacy</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="N2" t="n">
         <v>1510</v>
       </c>
@@ -731,7 +802,16 @@
       <c r="Q2" t="n">
         <v>19</v>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="T2" t="n">
         <v>517</v>
       </c>
@@ -769,7 +849,17 @@
       <c r="AF2" t="n">
         <v>0</v>
       </c>
-      <c r="AK2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="AL2" t="n">
         <v>2000</v>
       </c>
@@ -823,7 +913,11 @@
           <t>Construct Binary Tree from Preorder and Inorder Traversal</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>medium</t>
@@ -849,7 +943,21 @@
           <t>legacy</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="N3" t="n">
         <v>2355</v>
       </c>
@@ -862,7 +970,16 @@
       <c r="Q3" t="n">
         <v>27</v>
       </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="T3" t="n">
         <v>762</v>
       </c>
@@ -900,7 +1017,17 @@
       <c r="AF3" t="n">
         <v>0</v>
       </c>
-      <c r="AK3" t="inlineStr"/>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="AL3" t="n">
         <v>2753</v>
       </c>
@@ -932,6 +1059,906 @@
         <v>100</v>
       </c>
       <c r="AX3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6a5cfe0b-ead7-40f6-8e38-b866ccbbae9f</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-12 10:53:44</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Smallest Index With Digit Sum Equal to Index</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/smallest-index-with-digit-sum-equal-to-index/description/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>c0cf95285f54eaebedb9669a2aebe8239832722a8830a2e4215272d5a7af2264</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 3550 Name: Smallest Index With Digit Sum Equal to Index Difficulty: easy Link: https://leetcode.com/problems/smallest-index-with-digit-sum-equal-to-index/description/ Py...</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 3550
+Name: Smallest Index With Digit Sum Equal to Index
+Difficulty: easy
+Link: https://leetcode.com/problems/smallest-index-with-digit-sum-equal-to-index/description/
+Python Solution:
+class Solution:
+    def smallestIndex(self, nums: List[int]) -&gt; int:
+        def sumOfDigits(n: int, p: int):
+            presSum=0
+            while n &gt; 0:
+                presDigit = n%10
+                presSum += presDigit
+                n = n // 10
+            return presSum == p
+        for index,num in enumerate(nums):
+            if sumOfDigits(num,index):
+                return index
+        return -1
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1257</v>
+      </c>
+      <c r="O4" t="n">
+        <v>43</v>
+      </c>
+      <c r="P4" t="n">
+        <v>416</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>d1fc3b762e8bb16933e40b68d81c7ac883f5b7573dfa37378414dfb93ffab92e</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>class Solution:
+    def smallestIndex(self, nums: List[int]) -&gt; int:
+        def sumOfDigits(n: int, p: int):
+            presSum=0
+            while n &gt; 0:
+                presDigit = n%10
+                presSum += presDigit
+                n = n // 10
+            return presSum == p
+        for index,num in enumerate(nums):
+            if sumOfDigits(num,index):
+                return index
+        return -1</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>363</v>
+      </c>
+      <c r="U4" t="n">
+        <v>435</v>
+      </c>
+      <c r="V4" t="n">
+        <v>798</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.1983</v>
+      </c>
+      <c r="X4" t="n">
+        <v>144093.07</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>8202.32</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>40989.38</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>93763.81</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>4.6393</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1768</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Title: Easy LeetCode Problem Solution - Smallest Index With Digit Sum Equal to Index (Python) with Time-Optimized Approach (O(n))
+## Intuition
+The problem requires finding the smallest index `i` where the sum of digits in the number at that index equals `i`. This problem can be solved by creating a helper function `sumOfDigits()`, which calculates the sum of the digits in a given number, and then iterating through the input array, checking if the sum of digits of each number equals its index.
+## Approach
+1. Define the `sumOfDigits(n: int, p: int)` helper function that calculates the sum of the digits of a given number `n`, and checks if this sum equals the provided value `p`. The function calculates the sum by iteratively dividing `n` by 10 while keeping track of the sum of the remaining digits.
+2. Iterate through the input array `nums` using an enumeration, checking for each element whether its digit sum is equal to its index (i.e., if `sumOfDigits(num[index], index)` returns True). If such a number is found, return its index; otherwise, return -1.
+## Time Complexity
+The overall time complexity of this solution is O(n), as it relies on a single linear iteration through the input array `nums`. The helper function `sumOfDigits()` also performs a constant-time operation (dividing by 10 and taking the modulo) for each digit, but its total execution time remains constant as well due to the small number of digits involved.
+## Space Complexity
+The space complexity is O(1), since the helper function only requires a single local variable `presSum` to keep track of the sum of digits, and this variable does not occupy additional memory during the iteration through the input array. The total space usage remains constant throughout the execution.</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>2301</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>55a44ed8-3c31-4aef-8e06-be29380ccf3d</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-12 11:00:39</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3754</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Concatenate Non-Zero Digits and Multiply by Sum I</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/concatenate-non-zero-digits-and-multiply-by-sum-i/description/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0a14926d6f27abbf97fe7eb91c44afa2a689642cb201edf5f0dee7fe2301d460</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 3754 Name: Concatenate Non-Zero Digits and Multiply by Sum I Difficulty: easy Link: https://leetcode.com/problems/concatenate-non-zero-digits-and-multiply-by-sum-i/descr...</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 3754
+Name: Concatenate Non-Zero Digits and Multiply by Sum I
+Difficulty: easy
+Link: https://leetcode.com/problems/concatenate-non-zero-digits-and-multiply-by-sum-i/description/
+Python Solution:
+class Solution:
+    def sumAndMultiply(self, n: int) -&gt; int:
+        presSum = 0
+        presNo = ""
+        while n &gt; 0:
+            presDigit = n%10
+            if presDigit != 0:
+                presNo += str(presDigit)
+                presSum += presDigit
+            n = n//10
+        if presNo == "":
+            return 0
+        return int(presNo[::-1])*presSum
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1229</v>
+      </c>
+      <c r="O5" t="n">
+        <v>43</v>
+      </c>
+      <c r="P5" t="n">
+        <v>378</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>15</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0f7beb417846ed7d58427ff8d1c84cbf8c2ec9b45e9ed75eb212490ae98a1c84</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">class Solution:
+    def sumAndMultiply(self, n: int) -&gt; int:
+        presSum = 0
+        presNo = ""
+        while n &gt; 0:
+            presDigit = n%10
+            if presDigit != 0:
+                presNo += str(presDigit)
+                presSum += presDigit
+            n = n//10
+        if presNo == "":
+            return 0
+        return int(presNo[::-1])*presSum
+        </t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>369</v>
+      </c>
+      <c r="U5" t="n">
+        <v>428</v>
+      </c>
+      <c r="V5" t="n">
+        <v>797</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.1599</v>
+      </c>
+      <c r="X5" t="n">
+        <v>106617.12</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>5355.35</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>24325.91</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>76515.10000000001</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>5.5937</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1491</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Title: Concatenating Non-Zero Digits and Multiplying by Sum I (Easy) in Python - Big O Notation: O(k), where k is the number of non-zero digits in the input
+## Intuition
+The core idea is to iteratively process each digit of the given integer `n`. If a digit is non-zero, we add it to a running sum and concatenate it with a string `presNo`. In the end, we return the result of multiplying the reverse of `presNo` by `presSum`.
+## Approach
+1. Initialize two variables: `presSum` and an empty string `presNo`.
+2. While `n &gt; 0`, perform the following steps:
+   a. Calculate the remainder of `n` divided by 10, which gives us the current digit. If it's non-zero, we add it to `presSum`, concatenate it with `presNo`, and update `n` to be the quotient of the division (i.e., removing the last digit).
+   b. If the current digit is 0, there are no non-zero digits, so we return 0.
+3. After iterating through all the digits, we have `presNo` containing only the non-zero digits and `presSum` being their sum.
+4. Return the product of reversing `presNo` (by using a slice notation) and `presSum`.
+## Time Complexity
+The time complexity is O(k), where k is the number of non-zero digits in the input integer `n`. Each digit requires one iteration, and the total iterations are equal to the number of non-zero digits.
+## Space Complexity
+The space complexity is O(k) due to the additional space needed for storing non-zero digits in the string `presNo` and their sum in the variable `presSum`.</t>
+        </is>
+      </c>
+      <c r="AL5" t="n">
+        <v>1986</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>d72b3d39-9d73-46fb-bfaa-52998f459f39</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-12 11:15:43</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3803</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Count Residue Prefixes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/count-residue-prefixes/description/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>bc4d6a1b30057aeb421828e3058b67b393c68ef3e9a044f87d681c404bd8d7c3</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 3803 Name: Count Residue Prefixes Difficulty: easy Link: https://leetcode.com/problems/count-residue-prefixes/description/ Python Solution: class Solution: def residuePr...</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 3803
+Name: Count Residue Prefixes
+Difficulty: easy
+Link: https://leetcode.com/problems/count-residue-prefixes/description/
+Python Solution:
+class Solution:
+    def residuePrefixes(self, s: str) -&gt; int:
+        incurred = set()
+        result = 0
+        for index,ch in enumerate(s,start=1):
+            incurred.add(ch)
+            if len(incurred) == (index)%3:
+                result+=1
+        return result
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1070</v>
+      </c>
+      <c r="O6" t="n">
+        <v>39</v>
+      </c>
+      <c r="P6" t="n">
+        <v>273</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>11</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0616e3d2fd1afb62eb4190d385993c9b916b5b7f8457ab985dfe7d917bb3173a</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>class Solution:
+    def residuePrefixes(self, s: str) -&gt; int:
+        incurred = set()
+        result = 0
+        for index,ch in enumerate(s,start=1):
+            incurred.add(ch)
+            if len(incurred) == (index)%3:
+                result+=1
+        return result</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>313</v>
+      </c>
+      <c r="U6" t="n">
+        <v>296</v>
+      </c>
+      <c r="V6" t="n">
+        <v>609</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9457</v>
+      </c>
+      <c r="X6" t="n">
+        <v>72337.64999999999</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>5085.04</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20177.68</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>46903.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>6.3108</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1239</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Title: Count Residue Prefixes - Sliding Window Technique (O(n)) Solution in Python
+## Intuition
+The problem can be solved using the Sliding Window technique. We maintain a set to keep track of the characters encountered so far in the current window and count the number of residue prefixes by checking if the size of the set matches the index divided by 3, i.e., every third element of the sequence formed by the string's indices.
+## Approach
+1. Initialize an empty set to store the characters.
+2. Iterate through the input string `s`, starting from the second character (index 1) to avoid considering the initial character as a prefix.
+3. Add each character to the set during iteration and check if the size of the set matches the current index modulo 3. If it does, increment the count of residue prefixes.
+4. Return the final count of residue prefixes.
+## Time Complexity
+O(n) - Linear time complexity due to a single pass through the input string using the sliding window approach.
+## Space Complexity
+O(k) - Space complexity depends on the number of distinct characters in the input string (k). In the worst-case scenario, k could be equal to the length of the input string, but it is likely to be much smaller for typical inputs.</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>1629</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>b2e3c2ed-a564-457d-be1d-f5cb5c5da4a6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-12 11:21:20</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3492</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Maximum Containers on a Ship</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/maximum-containers-on-a-ship/description/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4136b715d00f86dbecec596bc2b3edd9d641459ca344c6cf63430eeb8a8d0479</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 3492 Name: Maximum Containers on a Ship Difficulty: easy Link: https://leetcode.com/problems/maximum-containers-on-a-ship/description/ Python Solution: class Solution: d...</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 3492
+Name: Maximum Containers on a Ship
+Difficulty: easy
+Link: https://leetcode.com/problems/maximum-containers-on-a-ship/description/
+Python Solution:
+class Solution:
+    def maxContainers(self, n: int, w: int, maxWeight: int) -&gt; int:
+        result = maxWeight // w
+        result = min(result, n**2)
+        return result
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>982</v>
+      </c>
+      <c r="O7" t="n">
+        <v>34</v>
+      </c>
+      <c r="P7" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ff8a92d44541e23edca2aa1b131eaff2af623fa15684ed25a2964446f1abc32c</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>class Solution:
+    def maxContainers(self, n: int, w: int, maxWeight: int) -&gt; int:
+        result = maxWeight // w
+        result = min(result, n**2)
+        return result</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>281</v>
+      </c>
+      <c r="U7" t="n">
+        <v>312</v>
+      </c>
+      <c r="V7" t="n">
+        <v>593</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.1103</v>
+      </c>
+      <c r="X7" t="n">
+        <v>66915.33</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>56.74</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>15227.79</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>51303.52</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>6.0815</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1412</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Title: Greedy Algorithm Based Solution for Maximum Containers on a Ship with O(1) Time Complexity
+## Intuition
+The problem can be approached using the Greedy Algorithm strategy where we initially assume that the ship can carry as many containers as possible (`n**2`) and then gradually decrease the number of containers based on the weight constraints. The intuition is to fill up the ship as much as possible before considering any weight limitations.
+## Approach
+1. Initialize `result` variable with the maximum number of containers that can be carried by the ship without considering weight constraints (i.e., `n**2`).
+2. Compute the total weight capacity of the ship using the weight of each container (`w`) and the initial number of containers (`result`). If this total weight exceeds the maximum allowable weight (`maxWeight`), then reduce the number of containers until the total weight fits within the limit.
+3. Return the final value of `result`, which represents the maximum number of containers that can be carried by the ship while respecting the weight constraints.
+## Time Complexity
+The time complexity of this solution is O(1), since it only involves constant-time arithmetic operations and variable assignments.
+## Space Complexity
+The space complexity of this solution is O(1), as a single variable `result` is used to store the maximum number of containers that can be carried by the ship.</t>
+        </is>
+      </c>
+      <c r="AL7" t="n">
+        <v>1702</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -966,7 +1993,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -976,7 +2003,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -1006,7 +2033,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.44</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="7">
@@ -1016,7 +2043,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>173727</v>
+        <v>122902.86</v>
       </c>
     </row>
     <row r="8">
@@ -1026,7 +2053,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>91.66</v>
+        <v>97.22</v>
       </c>
     </row>
     <row r="9">
@@ -1036,7 +2063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>96.67</v>
       </c>
     </row>
   </sheetData>
@@ -1050,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1127,6 +2154,154 @@
       </c>
       <c r="I2" t="n">
         <v>1.0014</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0a14926d6f27abbf97fe7eb91c44afa2a689642cb201edf5f0dee7fe2301d460</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.1599</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4136b715d00f86dbecec596bc2b3edd9d641459ca344c6cf63430eeb8a8d0479</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.1103</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bc4d6a1b30057aeb421828e3058b67b393c68ef3e9a044f87d681c404bd8d7c3</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9457</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>c0cf95285f54eaebedb9669a2aebe8239832722a8830a2e4215272d5a7af2264</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.1983</v>
       </c>
     </row>
   </sheetData>
@@ -1177,16 +2352,194 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>5.44</v>
+        <v>5.58</v>
       </c>
       <c r="D2" t="n">
-        <v>173727</v>
+        <v>122902.86</v>
       </c>
       <c r="E2" t="n">
-        <v>91.66</v>
+        <v>97.22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field / Value</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>prompt_strategy = 'legacy'</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Run logged before prompt strategy tracking was added (pre-v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>problem_link = '—'</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Problem link was not captured (pre-v2 run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>prompt_text = '—'</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Prompt text was not captured (pre-v2 run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>code_text = '—'</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Solution code was not captured (pre-v2 run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>llm_response_text = '—'</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Raw LLM response was not captured (pre-v2 run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>code_appended_externally = 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Code was appended locally (not generated by LLM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>llm_returned_code_block = 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LLM included a code block despite instructions not to</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>format_score</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Weighted score 0–100 based on presence of required markdown sections</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>completeness_score</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Percentage of required sections present in the output</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>output_input_ratio</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>response_tokens / prompt_tokens — higher = more verbose output</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tokens_per_sec</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LLM generation speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>All rows with '—' are legacy runs. Generate a new post to see fully-populated data.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/llm_stats/token_usage.xlsx
+++ b/llm_stats/token_usage.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX15"/>
+  <dimension ref="A1:AX33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="80" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
     <col width="66" customWidth="1" min="11" max="11"/>
@@ -3849,6 +3849,4482 @@
       </c>
       <c r="AX15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>c82b5bf6-31c1-4cdf-b4e0-6dafda745e47</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-15 09:19:05</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Island Perimeter</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/island-perimeter/description/</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>8944a6e3d66d520de1a9f90f5bc69b56f350f09fa6371ad15b7dd563c9d92afa</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 463 Name: Island Perimeter Difficulty: easy Link: https://leetcode.com/problems/island-perimeter/description/ Python Solution: class Solution: def islandPerimeter(self, ...</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 463
+Name: Island Perimeter
+Difficulty: easy
+Link: https://leetcode.com/problems/island-perimeter/description/
+Python Solution:
+class Solution:
+    def islandPerimeter(self, grid: List[List[int]]) -&gt; int:
+        rows = len(grid)
+        cols = len(grid[0])
+        result = 0
+        for i in range(rows):
+            for j in range(cols):
+                if grid[i][j] == 1:
+                    result += 4
+                    if i &gt; 0 and grid[i-1][j] == 1:
+                        result -= 2
+                    if j &gt; 0 and grid[i][j-1] == 1:
+                        result -= 2
+        return result
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>1361</v>
+      </c>
+      <c r="O16" t="n">
+        <v>45</v>
+      </c>
+      <c r="P16" t="n">
+        <v>480</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>16</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>4095d4749d2eeb726f99d0d2abd803e018fabc0d55c0a5c7620ce5081fc5347d</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>class Solution:
+    def islandPerimeter(self, grid: List[List[int]]) -&gt; int:
+        rows = len(grid)
+        cols = len(grid[0])
+        result = 0
+        for i in range(rows):
+            for j in range(cols):
+                if grid[i][j] == 1:
+                    result += 4
+                    if i &gt; 0 and grid[i-1][j] == 1:
+                        result -= 2
+                    if j &gt; 0 and grid[i][j-1] == 1:
+                        result -= 2
+        return result</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>396</v>
+      </c>
+      <c r="U16" t="n">
+        <v>324</v>
+      </c>
+      <c r="V16" t="n">
+        <v>720</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.8182</v>
+      </c>
+      <c r="X16" t="n">
+        <v>73633.92</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>5674.88</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>16205.38</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>51673.45</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>6.2701</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1298</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Title: Breadth-First Search (BFS) for Island Perimeter Problem in O(m+n) Time Complexity
+## Intuition
+The intuition behind this solution is to traverse each connected component (island) of the grid, count its perimeter pixels, and subtract the connected pixels to avoid double-counting.
+## Approach
+We iterate through every cell in the 2D grid. If a cell contains an island (1), we increment the total perimeter by 4 (one for each edge) and then check its adjacent cells to see if they also contain an island. If they do, we subtract 2 from the total perimeter count for each connected neighbor as it is no longer considered part of the island's perimeter.
+## Time Complexity
+The time complexity of this solution is O(m+n), where m and n are the number of rows and columns in the grid, respectively. This is due to iterating through every cell in the grid once, which takes O(m*n) time in total. The internal nested loops within the iteration have a combined linear complexity (O(k)), but since k (number of neighbors) remains constant for all cells, it can be absorbed into the m*n term.
+## Space Complexity
+The space complexity of this solution is O(1), as we only use a few variables to keep track of the total perimeter and grid dimensions, which do not grow with the size of the input.</t>
+        </is>
+      </c>
+      <c r="AL16" t="n">
+        <v>1873</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4b82067b-74cf-42d1-8bac-21d4a2085318</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-15 09:19:45</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Island Perimeter</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/island-perimeter/description/</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>8944a6e3d66d520de1a9f90f5bc69b56f350f09fa6371ad15b7dd563c9d92afa</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 463 Name: Island Perimeter Difficulty: easy Link: https://leetcode.com/problems/island-perimeter/description/ Python Solution: class Solution: def islandPerimeter(self, ...</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 463
+Name: Island Perimeter
+Difficulty: easy
+Link: https://leetcode.com/problems/island-perimeter/description/
+Python Solution:
+class Solution:
+    def islandPerimeter(self, grid: List[List[int]]) -&gt; int:
+        rows = len(grid)
+        cols = len(grid[0])
+        result = 0
+        for i in range(rows):
+            for j in range(cols):
+                if grid[i][j] == 1:
+                    result += 4
+                    if i &gt; 0 and grid[i-1][j] == 1:
+                        result -= 2
+                    if j &gt; 0 and grid[i][j-1] == 1:
+                        result -= 2
+        return result
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>1361</v>
+      </c>
+      <c r="O17" t="n">
+        <v>45</v>
+      </c>
+      <c r="P17" t="n">
+        <v>480</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>16</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>4095d4749d2eeb726f99d0d2abd803e018fabc0d55c0a5c7620ce5081fc5347d</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>class Solution:
+    def islandPerimeter(self, grid: List[List[int]]) -&gt; int:
+        rows = len(grid)
+        cols = len(grid[0])
+        result = 0
+        for i in range(rows):
+            for j in range(cols):
+                if grid[i][j] == 1:
+                    result += 4
+                    if i &gt; 0 and grid[i-1][j] == 1:
+                        result -= 2
+                    if j &gt; 0 and grid[i][j-1] == 1:
+                        result -= 2
+        return result</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>396</v>
+      </c>
+      <c r="U17" t="n">
+        <v>253</v>
+      </c>
+      <c r="V17" t="n">
+        <v>649</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.6389</v>
+      </c>
+      <c r="X17" t="n">
+        <v>100757.53</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>52.27</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>159.87</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>39647.87</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>6.3812</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1032</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Title: Breadth-First Search (BFS) approach to Island Perimeter Problem with O(m * n) Time Complexity and O(1) Space Complexity in Python
+## Intuition
+The intuition behind the solution is that we traverse each connected land (island) and count the number of edges. Each land has 4 potential edges, but if a neighboring cell is also land, it shares an edge with no perimeter to be counted.
+## Approach
+The implementation uses a straightforward BFS approach to traverse the grid. For each land found during traversal, we count the initial 4 edges and subtract 2 for each neighboring land (sharing an edge). The traversal starts from all land cells and continues until no more lands are found.
+## Time Complexity
+The time complexity of this solution is O(m * n) because we visit each grid cell exactly once during the BFS traversal.
+## Space Complexity
+The space complexity is O(1) due to using a simple stack data structure for the BFS traversal, which has a constant space requirement regardless of the size of the input grid.</t>
+        </is>
+      </c>
+      <c r="AL17" t="n">
+        <v>1558</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0043987e-4924-4662-b5ca-c430564345b7</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-15 17:15:36</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Cousins in Binary Tree</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/cousins-in-binary-tree/description/</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>b2f14c87a72a132a2e3abc1861c1aad0a5428c852cd6c1bb279ecc81e993b804</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 993 Name: Cousins in Binary Tree Difficulty: easy Link: https://leetcode.com/problems/cousins-in-binary-tree/description/ Python Solution: # Definition for a binary tree...</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 993
+Name: Cousins in Binary Tree
+Difficulty: easy
+Link: https://leetcode.com/problems/cousins-in-binary-tree/description/
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+from collections import deque
+class Solution:
+    def isCousins(self, root: Optional[TreeNode], x: int, y: int) -&gt; bool:
+        q = deque([root])
+        while q:
+            length = len(q)
+            found_x = False
+            found_y = False
+            for _ in range(length):
+                presNode = q.popleft()
+                if presNode.val == x:
+                    found_x = True
+                if presNode.val == y:
+                    found_y = True
+                if presNode.left and presNode.right:
+                    if (presNode.left.val == x and presNode.right.val == y) or (presNode.right.val == x and presNode.left.val == y):
+                        return False
+                if presNode.left:
+                    q.append(presNode.left)
+                if presNode.right:
+                    q.append(presNode.right)
+            if found_x and found_y:
+                return True
+            if found_x or found_y:
+                return False
+        return False
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2107</v>
+      </c>
+      <c r="O18" t="n">
+        <v>65</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1214</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>36</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>71d6ed6a3de30bb1f4ace73daf8a18f016956afbeadc66e187484d20b965d094</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+from collections import deque
+class Solution:
+    def isCousins(self, root: Optional[TreeNode], x: int, y: int) -&gt; bool:
+        q = deque([root])
+        while q:
+            length = len(q)
+            found_x = False
+            found_y = False
+            for _ in range(length):
+                presNode = q.popleft()
+                if presNode.val == x:
+                    found_x = True
+                if presNode.val == y:
+                    found_y = True
+                if presNode.left and presNode.right:
+                    if (presNode.left.val == x and presNode.right.val == y) or (presNode.right.val == x and presNode.left.val == y):
+                        return False
+                if presNode.left:
+                    q.append(presNode.left)
+                if presNode.right:
+                    q.append(presNode.right)
+            if found_x and found_y:
+                return True
+            if found_x or found_y:
+                return False
+        return False
+        </t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>593</v>
+      </c>
+      <c r="U18" t="n">
+        <v>480</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1073</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.8094</v>
+      </c>
+      <c r="X18" t="n">
+        <v>110462.52</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>6012.45</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>25108.57</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>79225.32000000001</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>6.0587</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1821</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Title: Breadth-First Search (BFS) Solution with Time and Space Complexity Analysis for LeetCode Problem 993 - Cousins in Binary Tree
+## Intuition
+The intuition behind this solution is to perform a level-order traversal (also known as breadth-first search, BFS) of the binary tree. We traverse each node at the same depth level and check if both `x` and `y` appear on the same level without being parents or children of each other. This ensures that they are not siblings nor ancestors, hence they must be cousins.
+## Approach
+1. Initialize a deque (double-ended queue) with the root node.
+2. Perform BFS by iteratively processing nodes at each depth level.
+3. Maintain two flags `found_x` and `found_y`, to check if we have found both `x` and `y` nodes during traversal.
+4. Check for each node, if it is either `x` or `y`, set the corresponding flag.
+5. Also, for every node encountered, verify that neither its left child nor right child can be the other cousin (i.e., `x` and `y` should not be siblings nor parents-children of each other).
+6. If both `x` and `y` are found during traversal on the same level, return `True`, signifying they are cousins. If either of them is encountered but not the other, or if they are found as siblings or parent-child nodes, return `False`.
+7. If no nodes are found during traversal (i.e., empty tree), return `False`.
+## Time Complexity
+The time complexity of this solution is O(h), where h represents the height of the binary tree since we perform a BFS operation. The BFS visits all nodes at each depth level, and we process each node only once.
+## Space Complexity
+The space complexity is O(h) as well due to the use of the deque data structure during the BFS traversal. Since we visit each node at most once, there will be at most h nodes in the queue at any given time.</t>
+        </is>
+      </c>
+      <c r="AL18" t="n">
+        <v>3086</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>66</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>8fb26d7f-b5b9-4895-b95f-f493c674b116</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-16 10:20:08</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Delete Leaves With a Given Value</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/delete-leaves-with-a-given-value/description/</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>071c654c972ce5bfb43253234ab1aeabba1b04671f650eaab6eed9b18245278d</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 1325 Name: Delete Leaves With a Given Value Difficulty: medium Link: https://leetcode.com/problems/delete-leaves-with-a-given-value/description/ Python Solution: # Defin...</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 1325
+Name: Delete Leaves With a Given Value
+Difficulty: medium
+Link: https://leetcode.com/problems/delete-leaves-with-a-given-value/description/
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def removeLeafNodes(self, root: Optional[TreeNode], target: int) -&gt; Optional[TreeNode]:
+        def dfs(root, target):
+            if not root:
+                return None
+            root.left = dfs(root.left,target)
+            root.right = dfs(root.right,target)
+            if not root.left and not root.right and root.val == target:
+                return None
+            return root
+        return dfs(root,target)
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>1583</v>
+      </c>
+      <c r="O19" t="n">
+        <v>52</v>
+      </c>
+      <c r="P19" t="n">
+        <v>667</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>23</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>6381fb0c2ac949c2afbbb932aa61f0e1ce81e19e2cc5718c219384d3143e9cdb</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def removeLeafNodes(self, root: Optional[TreeNode], target: int) -&gt; Optional[TreeNode]:
+        def dfs(root, target):
+            if not root:
+                return None
+            root.left = dfs(root.left,target)
+            root.right = dfs(root.right,target)
+            if not root.left and not root.right and root.val == target:
+                return None
+            return root
+        return dfs(root,target)</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>448</v>
+      </c>
+      <c r="U19" t="n">
+        <v>480</v>
+      </c>
+      <c r="V19" t="n">
+        <v>928</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.0714</v>
+      </c>
+      <c r="X19" t="n">
+        <v>103969.63</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>6767.8</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>18828.89</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>78249.10000000001</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>6.1343</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1962</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Title: Depth-First Search (DFS) with Value Removal Technique - O(n) Time Complexity and O(h) Space Complexity
+## Intuition
+The idea behind this solution is to remove leaves from a binary tree that have a value equal to the given target. We achieve this by performing a depth-first search (DFS), where during traversal, we check if the current node's value matches the target and remove it if it does. Furthermore, since we only need to traverse the branches with non-target nodes, we can stop traversing once we find a non-target node or reach an empty subtree.
+## Approach
+1. We define the main function `removeLeafNodes`, which takes in a root node and the target value as parameters.
+2. Inside this function, we create a helper function `dfs` that performs the actual traversal.
+3. In `dfs`, we first check if the current node is not empty; if not, we recursively call `dfs` on its left and right children.
+4. After traversing the children, we compare the value of the current node with the target. If they match, we return None to indicate that this leaf should be removed. Otherwise, we return the current node as-is.
+5. In the main function `removeLeafNodes`, we call `dfs` on the root node and the target value provided. The resulting tree will have all leaves with the target value removed.
+## Time Complexity
+The time complexity of this solution is O(n), where n represents the total number of nodes in the binary tree. This is because each node gets visited exactly once during the DFS traversal.
+## Space Complexity
+The space complexity for this solution is O(h), where h is the height of the given binary tree. The additional space required is due to recursion stack frames during the DFS traversal, which grow and shrink as we move deeper into the tree. Since every node has at most one child (either left or right), the height of a balanced binary tree is log2(n) (in the worst case scenario). Therefore, the space complexity is O(log2(n)).</t>
+        </is>
+      </c>
+      <c r="AL19" t="n">
+        <v>2703</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>51</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8c2f0ab5-53ab-48ad-a869-173d7a65d3c4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-16 10:20:58</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Delete Leaves With a Given Value</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/delete-leaves-with-a-given-value/description/</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>071c654c972ce5bfb43253234ab1aeabba1b04671f650eaab6eed9b18245278d</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 1325 Name: Delete Leaves With a Given Value Difficulty: medium Link: https://leetcode.com/problems/delete-leaves-with-a-given-value/description/ Python Solution: # Defin...</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 1325
+Name: Delete Leaves With a Given Value
+Difficulty: medium
+Link: https://leetcode.com/problems/delete-leaves-with-a-given-value/description/
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def removeLeafNodes(self, root: Optional[TreeNode], target: int) -&gt; Optional[TreeNode]:
+        def dfs(root, target):
+            if not root:
+                return None
+            root.left = dfs(root.left,target)
+            root.right = dfs(root.right,target)
+            if not root.left and not root.right and root.val == target:
+                return None
+            return root
+        return dfs(root,target)
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>1583</v>
+      </c>
+      <c r="O20" t="n">
+        <v>52</v>
+      </c>
+      <c r="P20" t="n">
+        <v>667</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>23</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>6381fb0c2ac949c2afbbb932aa61f0e1ce81e19e2cc5718c219384d3143e9cdb</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def removeLeafNodes(self, root: Optional[TreeNode], target: int) -&gt; Optional[TreeNode]:
+        def dfs(root, target):
+            if not root:
+                return None
+            root.left = dfs(root.left,target)
+            root.right = dfs(root.right,target)
+            if not root.left and not root.right and root.val == target:
+                return None
+            return root
+        return dfs(root,target)</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>448</v>
+      </c>
+      <c r="U20" t="n">
+        <v>317</v>
+      </c>
+      <c r="V20" t="n">
+        <v>765</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.7076</v>
+      </c>
+      <c r="X20" t="n">
+        <v>117791.99</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>51.04</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>164.05</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>50566.62</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>6.269</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1343</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Title: Depth-First Search (DFS) with Target Value Removal in Tree (O(N))
+## Intuition
+The solution utilizes Depth-First Search (DFS) to traverse the binary tree and remove any leaf nodes that have a value equal to the given target. The DFS approach allows us to explore all the nodes of the tree systematically while keeping track of the subtrees.
+## Approach
+The DFS function takes the root node and target value as input, recursively explores the left and right subtrees, and updates the current node accordingly. If a leaf node is found with the target value, it is removed from the tree by returning `None`. The rest of the nodes are passed along to their parent during the traversal.
+## Time Complexity
+The time complexity of this approach is O(N), where N is the number of nodes in the binary tree. This is due to the recursive nature of the DFS, which visits each node once and performs constant-time operations on each node.
+## Space Complexity
+The space complexity of this solution is O(H), where H is the height of the binary tree. The recursive function calls use a call stack that requires storage proportional to the depth of the longest path in the tree. However, since most real-world trees are balanced or nearly balanced, the space requirement is typically small compared to the number of nodes in the tree (O(log N)).</t>
+        </is>
+      </c>
+      <c r="AL20" t="n">
+        <v>2111</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>47</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>38cc7c12-c04d-438e-acb2-1d2250996f67</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-16 10:22:11</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Delete Leaves With a Given Value</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/delete-leaves-with-a-given-value/description/</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>071c654c972ce5bfb43253234ab1aeabba1b04671f650eaab6eed9b18245278d</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 1325 Name: Delete Leaves With a Given Value Difficulty: medium Link: https://leetcode.com/problems/delete-leaves-with-a-given-value/description/ Python Solution: # Defin...</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 1325
+Name: Delete Leaves With a Given Value
+Difficulty: medium
+Link: https://leetcode.com/problems/delete-leaves-with-a-given-value/description/
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def removeLeafNodes(self, root: Optional[TreeNode], target: int) -&gt; Optional[TreeNode]:
+        def dfs(root, target):
+            if not root:
+                return None
+            root.left = dfs(root.left,target)
+            root.right = dfs(root.right,target)
+            if not root.left and not root.right and root.val == target:
+                return None
+            return root
+        return dfs(root,target)
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>1583</v>
+      </c>
+      <c r="O21" t="n">
+        <v>52</v>
+      </c>
+      <c r="P21" t="n">
+        <v>667</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>23</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>6381fb0c2ac949c2afbbb932aa61f0e1ce81e19e2cc5718c219384d3143e9cdb</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def removeLeafNodes(self, root: Optional[TreeNode], target: int) -&gt; Optional[TreeNode]:
+        def dfs(root, target):
+            if not root:
+                return None
+            root.left = dfs(root.left,target)
+            root.right = dfs(root.right,target)
+            if not root.left and not root.right and root.val == target:
+                return None
+            return root
+        return dfs(root,target)</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>448</v>
+      </c>
+      <c r="U21" t="n">
+        <v>387</v>
+      </c>
+      <c r="V21" t="n">
+        <v>835</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.8638</v>
+      </c>
+      <c r="X21" t="n">
+        <v>156675</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>73.06</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>168.28</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>72707.75</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>5.3227</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1588</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Title: Depth-First Search (DFS) with In-place Deletion to Remove Leaves with a Given Value (Time Complexity: O(n))
+## Intuition
+The given solution uses Depth-First Search (DFS) technique, starting from the root node of the tree. It visits each node, checks if it has any children, and if its value matches the target. If a leaf node matches the criteria, it is removed in-place, i.e., the memory occupied by that node is freed.
+## Approach
+The DFS function takes two arguments: the current root node and the target value. It first checks if the root is `None`, meaning the tree is empty. If not, it recursively calls the DFS function for the left and right subtrees. After that, it checks if the current node has no children (both left and right subtrees are `None`) and its value equals the target. In such a case, it returns `None`, effectively removing the leaf node from the tree.
+## Time Complexity
+The time complexity of this solution is O(n), where n is the number of nodes in the binary tree. This is because each node is visited once during the DFS traversal. The recursive calls and branches (left, right) do not increase the complexity beyond linear.
+## Space Complexity
+The space complexity of this solution is O(h), where h is the height of the tree. In the worst-case scenario, the entire tree forms a linked list, making its height equivalent to the number of nodes (n). However, since only one extra recursive call is made at each level (left and right subtrees), space consumption remains roughly proportional to the tree's height rather than the number of nodes.</t>
+        </is>
+      </c>
+      <c r="AL21" t="n">
+        <v>2324</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>47</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>b3464399-3d31-40a5-8969-0c3d6dca68a2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-16 10:23:10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Delete Leaves With a Given Value</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/delete-leaves-with-a-given-value/description/</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>071c654c972ce5bfb43253234ab1aeabba1b04671f650eaab6eed9b18245278d</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 1325 Name: Delete Leaves With a Given Value Difficulty: medium Link: https://leetcode.com/problems/delete-leaves-with-a-given-value/description/ Python Solution: # Defin...</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 1325
+Name: Delete Leaves With a Given Value
+Difficulty: medium
+Link: https://leetcode.com/problems/delete-leaves-with-a-given-value/description/
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def removeLeafNodes(self, root: Optional[TreeNode], target: int) -&gt; Optional[TreeNode]:
+        def dfs(root, target):
+            if not root:
+                return None
+            root.left = dfs(root.left,target)
+            root.right = dfs(root.right,target)
+            if not root.left and not root.right and root.val == target:
+                return None
+            return root
+        return dfs(root,target)
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>1583</v>
+      </c>
+      <c r="O22" t="n">
+        <v>52</v>
+      </c>
+      <c r="P22" t="n">
+        <v>667</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>23</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>6381fb0c2ac949c2afbbb932aa61f0e1ce81e19e2cc5718c219384d3143e9cdb</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def removeLeafNodes(self, root: Optional[TreeNode], target: int) -&gt; Optional[TreeNode]:
+        def dfs(root, target):
+            if not root:
+                return None
+            root.left = dfs(root.left,target)
+            root.right = dfs(root.right,target)
+            if not root.left and not root.right and root.val == target:
+                return None
+            return root
+        return dfs(root,target)</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>448</v>
+      </c>
+      <c r="U22" t="n">
+        <v>357</v>
+      </c>
+      <c r="V22" t="n">
+        <v>805</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.7969000000000001</v>
+      </c>
+      <c r="X22" t="n">
+        <v>185250.53</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>51.49</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>170.05</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>57907.65</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>6.165</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1462</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Title: Depth-First Search (DFS) Based Solution with Linear Time Complexity (O(n)) for Deleting Leaves with a Given Value on Binary Tree
+## Intuition
+The solution utilizes the Depth-First Search (DFS) technique to traverse the binary tree and remove leaves that have the target value. The DFS algorithm explores all the nodes in the tree, allowing us to visit each leaf node only once.
+## Approach
+A helper function `dfs` is defined that takes a root node and the target value as input parameters. The function traverses the tree using recursion, visiting the left and right subtrees of the current node. If the node itself has the target value, it is removed and returns None. Otherwise, it updates the node's left and right subtrees with the results from the DFS recursive calls on those subtrees. The main function `removeLeafNodes` initializes the root node and calls the helper function to delete the leaf nodes that have the target value.
+## Time Complexity
+The time complexity of this solution is O(n), where n is the number of nodes in the binary tree, as we visit each node only once during the DFS traversal.
+## Space Complexity
+The space complexity of this solution is O(h), where h is the height of the binary tree, due to the recursive calls stack during the DFS traversal. However, since the binary tree is balanced on average (i.e., height ≈ log n), the space complexity can also be considered linear in terms of the number of nodes (O(n)).</t>
+        </is>
+      </c>
+      <c r="AL22" t="n">
+        <v>2176</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>47</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>a1506013-b6e5-40eb-87c7-7f8eaa940d4a</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-16 10:24:39</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1448</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Count Good Nodes in Binary Tree</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/count-good-nodes-in-binary-tree/description</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>3d5a72e71d90f5dbbc8ed308b88f196daaca5231c897266832ca16c27d210921</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 1448 Name: Count Good Nodes in Binary Tree Difficulty: medium Link: https://leetcode.com/problems/count-good-nodes-in-binary-tree/description Python Solution: # Definiti...</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 1448
+Name: Count Good Nodes in Binary Tree
+Difficulty: medium
+Link: https://leetcode.com/problems/count-good-nodes-in-binary-tree/description
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def goodNodes(self, root: TreeNode) -&gt; int:
+        def dfs(root: TreeNode, maxTillPath: int):
+            if not root:
+                return 0
+            count = 0
+            if root.val &gt;= maxTillPath:
+                count = 1
+                maxTillPath = root.val
+            count += dfs(root.left, maxTillPath)
+            count += dfs(root.right, maxTillPath)
+            return count
+        return dfs(root,root.val)
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1556</v>
+      </c>
+      <c r="O23" t="n">
+        <v>50</v>
+      </c>
+      <c r="P23" t="n">
+        <v>643</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>21</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>f69ff39112cca87fa96f26b19ae9d79b828e1d3e050d693c113c7ee212cbb59d</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def goodNodes(self, root: TreeNode) -&gt; int:
+        def dfs(root: TreeNode, maxTillPath: int):
+            if not root:
+                return 0
+            count = 0
+            if root.val &gt;= maxTillPath:
+                count = 1
+                maxTillPath = root.val
+            count += dfs(root.left, maxTillPath)
+            count += dfs(root.right, maxTillPath)
+            return count
+        return dfs(root,root.val)</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>453</v>
+      </c>
+      <c r="U23" t="n">
+        <v>404</v>
+      </c>
+      <c r="V23" t="n">
+        <v>857</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.8918</v>
+      </c>
+      <c r="X23" t="n">
+        <v>268794.23</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>23681.22</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>65375.17</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>6.1797</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1669</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Title: Depth-First Search (DFS) based Solution with Logarithmic Time Complexity (O(n)) in Python
+## Intuition
+The problem asks us to count all nodes in a binary tree that are greater than or equal to the maximum value encountered during a depth-first search from that node. We achieve this by performing a Depth-First Search (DFS) and maintaining a variable `maxTillPath` which keeps track of the maximum value found so far in the path from the root to the current node. If the current node's value is greater than or equal to `maxTillPath`, we increment the count and update `maxTillPath`.
+## Approach
+The approach involves defining a helper DFS function which takes in the current node and the maximum value found so far (`maxTillPath`). The function recursively explores the left and right subtrees, keeping track of the good nodes (i.e., nodes whose values are greater than or equal to `maxTillPath`) using the count variable. The base case for the DFS occurs when the node is null, in which case the function returns 0.
+The main function initializes the solution by calling the DFS function on the root of the tree with the root's value as the initial maximum value (`maxTillPath = root.val`). The final count returned from the DFS call represents the total number of good nodes in the binary tree.
+## Time Complexity
+The time complexity of this solution is O(n) due to the depth-first traversal, where n is the number of nodes in the binary tree. The space complexity is O(h), where h is the height of the binary tree (excluding the root node). This is because the recursive stack can grow up to a maximum depth equivalent to the height of the binary tree.</t>
+        </is>
+      </c>
+      <c r="AL23" t="n">
+        <v>2399</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>43</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>85</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="AX23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>16e74959-9b2f-4493-9b60-0093be346109</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-16 10:26:01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Smallest String Starting From Leaf</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/smallest-string-starting-from-leaf/description/</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>c3baa2bab00bbad49e25049de671efa0bb40f733999fc9f33b25ef16add7f7ff</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 988 Name: Smallest String Starting From Leaf Difficulty: medium Link: https://leetcode.com/problems/smallest-string-starting-from-leaf/description/ Python Solution: # De...</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 988
+Name: Smallest String Starting From Leaf
+Difficulty: medium
+Link: https://leetcode.com/problems/smallest-string-starting-from-leaf/description/
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def smallestFromLeaf(self, root: Optional[TreeNode]) -&gt; str:
+        self.smallest = '~'
+        def dfs(root, presStr):
+            if not root:
+                return
+            presChr = chr(ord('a')+root.val)
+            presStr += presChr
+            if not root.left and not root.right:
+                presStr = presStr[::-1]
+                self.smallest = min(self.smallest,presStr)
+            dfs(root.left,presStr)
+            dfs(root.right,presStr)
+            return
+        dfs(root,"")
+        return self.smallest
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>1678</v>
+      </c>
+      <c r="O24" t="n">
+        <v>54</v>
+      </c>
+      <c r="P24" t="n">
+        <v>759</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>25</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>72431cde96445ba3930f66a9eec7117ad90de7696ccffc0532a8738e7ff3fe1c</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def smallestFromLeaf(self, root: Optional[TreeNode]) -&gt; str:
+        self.smallest = '~'
+        def dfs(root, presStr):
+            if not root:
+                return
+            presChr = chr(ord('a')+root.val)
+            presStr += presChr
+            if not root.left and not root.right:
+                presStr = presStr[::-1]
+                self.smallest = min(self.smallest,presStr)
+            dfs(root.left,presStr)
+            dfs(root.right,presStr)
+            return
+        dfs(root,"")
+        return self.smallest</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>486</v>
+      </c>
+      <c r="U24" t="n">
+        <v>365</v>
+      </c>
+      <c r="V24" t="n">
+        <v>851</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="X24" t="n">
+        <v>82436.55</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>24075.79</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>58245.19</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>6.2666</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1589</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Title: Depth-First Search with Minimum String Construction using Binary Tree - O(N) Time Complexity and O(N) Space Complexity
+## Intuition
+The core idea is to traverse the binary tree from leaves to root using Depth-First Search (DFS), constructing a string by appending characters (in alphabetical order) as we visit each node. At each leaf, we compare the constructed string with the current minimum and store the smaller one.
+## Approach
+We define a helper function `dfs` that takes a tree node and a partial string as input. If the node is empty, it returns without doing anything. Otherwise, it appends the character for the current node (in alphabetical order) to the provided string, traverses the left and right subtrees recursively, and if the current node is a leaf, checks if the constructed string is smaller than the current minimum and updates it accordingly.
+The main function initializes the smallest string as a special character ('~'), calls `dfs` with the root node and an empty string, and finally returns the smallest string found during the traversal.
+## Time Complexity
+Since we traverse each node only once (due to DFS), the time complexity is O(N) where N is the number of nodes in the tree.
+## Space Complexity
+The additional space required for storing the current string and the minimum string is proportional to the depth of the tree, which can be as large as the number of nodes (in case of a complete binary tree). However, since we are only interested in the smallest string, the actual space complexity is O(N) when considering the worst-case scenario.</t>
+        </is>
+      </c>
+      <c r="AL24" t="n">
+        <v>2406</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>47</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3be228a5-81ca-4bc3-9430-3f99badc046d</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-16 10:27:18</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Univalued Binary Tree</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/univalued-binary-tree/description/</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1d39be7f1c9afc0becad95d70398e1199d81e9814065a0d4100a55b2bc455423</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 965 Name: Univalued Binary Tree Difficulty: easy Link: https://leetcode.com/problems/univalued-binary-tree/description/ Python Solution: # Definition for a binary tree n...</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 965
+Name: Univalued Binary Tree
+Difficulty: easy
+Link: https://leetcode.com/problems/univalued-binary-tree/description/
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def isUnivalTree(self, root: Optional[TreeNode]) -&gt; bool:
+        if not root:
+            return True
+        inOrderList = set()
+        def inOrder(root):
+            if not root:
+                return
+            nonlocal inOrderList
+            inOrder(root.left)
+            inOrderList.add(root.val)
+            inOrder(root.right)
+            return
+        inOrder(root)
+        return len(inOrderList) == 1
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>1530</v>
+      </c>
+      <c r="O25" t="n">
+        <v>52</v>
+      </c>
+      <c r="P25" t="n">
+        <v>639</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>23</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>00ee047bf03bc919c2518b793b85f9144758817788fb65bd199f82ad086aa488</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def isUnivalTree(self, root: Optional[TreeNode]) -&gt; bool:
+        if not root:
+            return True
+        inOrderList = set()
+        def inOrder(root):
+            if not root:
+                return
+            nonlocal inOrderList
+            inOrder(root.left)
+            inOrderList.add(root.val)
+            inOrder(root.right)
+            return
+        inOrder(root)
+        return len(inOrderList) == 1</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>433</v>
+      </c>
+      <c r="U25" t="n">
+        <v>352</v>
+      </c>
+      <c r="V25" t="n">
+        <v>785</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.8129</v>
+      </c>
+      <c r="X25" t="n">
+        <v>76816.71000000001</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>21053.48</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>55653.35</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>6.3249</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1420</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Title: Univalued Binary Tree Recursive Solution with Linear Time Complexity (O(n)) in Python
+## Intuition
+The core idea behind this solution is to traverse the binary tree using an In-order traversal while maintaining a set of distinct values. A univalued binary tree implies that all nodes in the tree have the same value, except for the root node's children, if any. By checking the size of the obtained set (which should contain only one element), we can determine whether the given tree is univalued or not.
+## Approach
+1. Implement a helper function `inOrder(root)` to traverse the binary tree in an In-order fashion and add each node's value to a set.
+2. Define the main function `isUnivalTree(root)` that calls the helper function, checks if the size of the obtained set is equal to 1, and returns the result accordingly.
+3. If not provided, initialize the tree with default values (val=0, left=None, right=None).
+## Time Complexity
+The time complexity for this solution is linear (O(n)) due to the In-order traversal that visits each node exactly once.
+## Space Complexity
+In addition to the original input tree's space requirement, this solution requires O(h) space for the set used during in-order traversal, where h is the height of the tree (assuming no duplicates). Since we only traverse one half of the binary tree while constructing the set, the actual space complexity is approximately O(log n).</t>
+        </is>
+      </c>
+      <c r="AL25" t="n">
+        <v>2150</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>49</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>a2e0c49a-558c-4f62-a6c6-3f62d773c955</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-16 10:44:09</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1609</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Even Odd Tree</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/even-odd-tree/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>41481490a920810238bce3157c26c7d16effddcebfa166c14a40b6953e1407a4</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 1609 Name: Even Odd Tree Difficulty: medium Link: https://leetcode.com/problems/even-odd-tree/ Python Solution: # Definition for a binary tree node. # class TreeNode: # ...</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 1609
+Name: Even Odd Tree
+Difficulty: medium
+Link: https://leetcode.com/problems/even-odd-tree/
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+from collections import deque
+class Solution:
+    def isEvenOddTree(self, root: Optional[TreeNode]) -&gt; bool:
+        if not root:
+            return True
+        q = deque([root])
+        level = 0
+        while q:
+            if level % 2 == 0:
+                prev = float('-inf')
+            else:
+                prev = float('inf')
+            length = len(q)
+            for _ in range(length):
+                presNode = q.popleft()
+                # even level
+                if level % 2 == 0:
+                    if presNode.val % 2 == 0 or presNode.val &lt;= prev:
+                        return False
+                # odd level
+                else:
+                    if presNode.val % 2 == 1 or presNode.val &gt;= prev:
+                        return False
+                prev = presNode.val
+                if presNode.left:
+                    q.append(presNode.left)
+                if presNode.right:
+                    q.append(presNode.right)
+            level += 1
+        return True
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>2073</v>
+      </c>
+      <c r="O26" t="n">
+        <v>76</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1207</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>47</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>a07303eb338435cfbcc8b95ba96a9572f67d8578d09accffbd3a61984be73712</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+from collections import deque
+class Solution:
+    def isEvenOddTree(self, root: Optional[TreeNode]) -&gt; bool:
+        if not root:
+            return True
+        q = deque([root])
+        level = 0
+        while q:
+            if level % 2 == 0:
+                prev = float('-inf')
+            else:
+                prev = float('inf')
+            length = len(q)
+            for _ in range(length):
+                presNode = q.popleft()
+                # even level
+                if level % 2 == 0:
+                    if presNode.val % 2 == 0 or presNode.val &lt;= prev:
+                        return False
+                # odd level
+                else:
+                    if presNode.val % 2 == 1 or presNode.val &gt;= prev:
+                        return False
+                prev = presNode.val
+                if presNode.left:
+                    q.append(presNode.left)
+                if presNode.right:
+                    q.append(presNode.right)
+            level += 1
+        return True</t>
+        </is>
+      </c>
+      <c r="T26" t="n">
+        <v>585</v>
+      </c>
+      <c r="U26" t="n">
+        <v>329</v>
+      </c>
+      <c r="V26" t="n">
+        <v>914</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.5624</v>
+      </c>
+      <c r="X26" t="n">
+        <v>85324.78</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>6770.4</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>24600.97</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>53867.7</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>6.1076</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1256</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Title: Breadth-first Search with Level Detection for Even-Odd Tree (Medium) - O(N) Time Complexity, O(H) Space Complexity
+## Intuition
+The solution checks if a given binary tree is an even-odd tree by traversing the tree level by level. At each level, nodes are either all even or all odd values. This property guarantees that if we find an inconsistency (e.g., an even node with a smaller odd value in the same level), then the tree cannot be an even-odd tree.
+## Approach
+The approach uses Breadth-First Search (BFS) to traverse the binary tree level by level. We maintain the current level and use a deque (double-ended queue) to store nodes at each level. For each node, we compare its value with the previous node's value in the same level to check for inconsistencies.
+## Time Complexity
+The time complexity of the solution is O(N), where N is the number of nodes in the tree. This is because we traverse all nodes once during BFS.
+## Space Complexity
+The space complexity of the solution is O(H), where H is the height of the tree. We use a deque to store nodes at each level, and its size can be equal to the maximum level in the tree, i.e., the tree's height. This memory usage is proportional to the depth of the deepest node in the tree.</t>
+        </is>
+      </c>
+      <c r="AL26" t="n">
+        <v>2525</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>71</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7637024b-9213-4758-9760-4877d0f5463b</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-17 00:11:07</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2583</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Kth Largest Sum in a Binary Tree</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/kth-largest-sum-in-a-binary-tree/description</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>4578943269ae09a8ccaef13e095ad921bb5df0504fdd5fcc149d32a847992766</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 2583 Name: Kth Largest Sum in a Binary Tree Difficulty: medium Link: https://leetcode.com/problems/kth-largest-sum-in-a-binary-tree/description Python Solution: # Defini...</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 2583
+Name: Kth Largest Sum in a Binary Tree
+Difficulty: medium
+Link: https://leetcode.com/problems/kth-largest-sum-in-a-binary-tree/description
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+from collections import deque
+class Solution:
+    def kthLargestLevelSum(self, root: Optional[TreeNode], k: int) -&gt; int:
+        result = []
+        q = deque([root])
+        while q:
+            presSum = 0
+            length = len(q)
+            for _ in range(length):
+                presNode = q.popleft()
+                presSum += presNode.val
+                if presNode.left:
+                    q.append(presNode.left)
+                if presNode.right:
+                    q.append(presNode.right)
+            result.append(presSum)
+        presLen = len(result)
+        if presLen &lt; k:
+            return -1
+        result.sort()
+        return result[-k]
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>1778</v>
+      </c>
+      <c r="O27" t="n">
+        <v>60</v>
+      </c>
+      <c r="P27" t="n">
+        <v>863</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>31</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>dc75fa5dadfe35973fc50e0c36a69e38ab17888700755ffc85652438a98806ad</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+from collections import deque
+class Solution:
+    def kthLargestLevelSum(self, root: Optional[TreeNode], k: int) -&gt; int:
+        result = []
+        q = deque([root])
+        while q:
+            presSum = 0
+            length = len(q)
+            for _ in range(length):
+                presNode = q.popleft()
+                presSum += presNode.val
+                if presNode.left:
+                    q.append(presNode.left)
+                if presNode.right:
+                    q.append(presNode.right)
+            result.append(presSum)
+        presLen = len(result)
+        if presLen &lt; k:
+            return -1
+        result.sort()
+        return result[-k]</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
+        <v>516</v>
+      </c>
+      <c r="U27" t="n">
+        <v>295</v>
+      </c>
+      <c r="V27" t="n">
+        <v>811</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.5717</v>
+      </c>
+      <c r="X27" t="n">
+        <v>75581.61</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>5635.39</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>22131.79</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>47740.86</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>6.1792</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1221</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Title: Breadth-First Search with Sum Calculation (Big O: O(N))
+## Intuition
+The idea is to traverse the binary tree using a breadth-first search (BFS) approach, while calculating the sum of values at each level. We store these sums in an array and find the kth largest sum from this array. This approach ensures we visit all nodes once, making it efficient.
+## Approach
+We use a deque to maintain the order of nodes to be visited during the BFS traversal. At each step, we calculate the sum of values at the current level, add it to a result array, and continue with the next level until there are no more nodes left in that level. Finally, we sort the result array and find the kth largest element.
+## Time Complexity
+The time complexity is O(N), where N is the number of nodes in the binary tree. This is because each node is visited once during the BFS traversal.
+## Space Complexity
+The space complexity is also O(N) due to the additional space required to store the sums at each level (result array). However, this can be optimized by using a single variable to calculate the sum instead of an array, reducing the space complexity to O(1) in practice. This optimized version would not affect the time complexity.</t>
+        </is>
+      </c>
+      <c r="AL27" t="n">
+        <v>2185</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>51</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>c9c45717-1b18-49db-b6c3-466744a937fa</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-17 00:11:57</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2583</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Kth Largest Sum in a Binary Tree</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/kth-largest-sum-in-a-binary-tree/description</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>4578943269ae09a8ccaef13e095ad921bb5df0504fdd5fcc149d32a847992766</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 2583 Name: Kth Largest Sum in a Binary Tree Difficulty: medium Link: https://leetcode.com/problems/kth-largest-sum-in-a-binary-tree/description Python Solution: # Defini...</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 2583
+Name: Kth Largest Sum in a Binary Tree
+Difficulty: medium
+Link: https://leetcode.com/problems/kth-largest-sum-in-a-binary-tree/description
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+from collections import deque
+class Solution:
+    def kthLargestLevelSum(self, root: Optional[TreeNode], k: int) -&gt; int:
+        result = []
+        q = deque([root])
+        while q:
+            presSum = 0
+            length = len(q)
+            for _ in range(length):
+                presNode = q.popleft()
+                presSum += presNode.val
+                if presNode.left:
+                    q.append(presNode.left)
+                if presNode.right:
+                    q.append(presNode.right)
+            result.append(presSum)
+        presLen = len(result)
+        if presLen &lt; k:
+            return -1
+        result.sort()
+        return result[-k]
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>1778</v>
+      </c>
+      <c r="O28" t="n">
+        <v>60</v>
+      </c>
+      <c r="P28" t="n">
+        <v>863</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>31</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>dc75fa5dadfe35973fc50e0c36a69e38ab17888700755ffc85652438a98806ad</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+from collections import deque
+class Solution:
+    def kthLargestLevelSum(self, root: Optional[TreeNode], k: int) -&gt; int:
+        result = []
+        q = deque([root])
+        while q:
+            presSum = 0
+            length = len(q)
+            for _ in range(length):
+                presNode = q.popleft()
+                presSum += presNode.val
+                if presNode.left:
+                    q.append(presNode.left)
+                if presNode.right:
+                    q.append(presNode.right)
+            result.append(presSum)
+        presLen = len(result)
+        if presLen &lt; k:
+            return -1
+        result.sort()
+        return result[-k]</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
+        <v>516</v>
+      </c>
+      <c r="U28" t="n">
+        <v>296</v>
+      </c>
+      <c r="V28" t="n">
+        <v>812</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.5736</v>
+      </c>
+      <c r="X28" t="n">
+        <v>89525.42</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>66.58</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>162.56</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>48959.79</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>6.0458</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1154</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Title: Level-Order DFS with Sorting - O(N) Time &amp; O(H) Space
+## Intuition
+The problem requires finding the kth largest sum of any level in a binary tree. We use Depth-First Search (DFS) via Breadth First Search (BFS) approach, traversing each level from left to right and keeping track of the sum of nodes at each level. After obtaining all sums, we sort them and return the kth largest value.
+## Approach
+We create a queue to store nodes at the current level during the BFS traversal. For each node visited, we update the partial sum for the current level, adding the node's value. When moving on to the next level, the partial sum is stored in a list (result) and the process repeats until all nodes are visited.
+Finally, we sort the result array, and return the kth largest element, checking if it exceeds the number of levels (N). If more than k levels were traversed, the solution returns -1.
+## Time Complexity
+- The time complexity is O(N) as each node is visited once.
+## Space Complexity
+- The space complexity is O(H) where H is the height of the binary tree, due to the use of a queue to store nodes at the current level during traversal.</t>
+        </is>
+      </c>
+      <c r="AL28" t="n">
+        <v>2118</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>53</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>39d42135-c7ed-4645-a2e4-1a685c52c016</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-17 00:12:59</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2583</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Kth Largest Sum in a Binary Tree</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/kth-largest-sum-in-a-binary-tree/description</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>4578943269ae09a8ccaef13e095ad921bb5df0504fdd5fcc149d32a847992766</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 2583 Name: Kth Largest Sum in a Binary Tree Difficulty: medium Link: https://leetcode.com/problems/kth-largest-sum-in-a-binary-tree/description Python Solution: # Defini...</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 2583
+Name: Kth Largest Sum in a Binary Tree
+Difficulty: medium
+Link: https://leetcode.com/problems/kth-largest-sum-in-a-binary-tree/description
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+from collections import deque
+class Solution:
+    def kthLargestLevelSum(self, root: Optional[TreeNode], k: int) -&gt; int:
+        result = []
+        q = deque([root])
+        while q:
+            presSum = 0
+            length = len(q)
+            for _ in range(length):
+                presNode = q.popleft()
+                presSum += presNode.val
+                if presNode.left:
+                    q.append(presNode.left)
+                if presNode.right:
+                    q.append(presNode.right)
+            result.append(presSum)
+        presLen = len(result)
+        if presLen &lt; k:
+            return -1
+        result.sort()
+        return result[-k]
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>1778</v>
+      </c>
+      <c r="O29" t="n">
+        <v>60</v>
+      </c>
+      <c r="P29" t="n">
+        <v>863</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>31</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>dc75fa5dadfe35973fc50e0c36a69e38ab17888700755ffc85652438a98806ad</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+from collections import deque
+class Solution:
+    def kthLargestLevelSum(self, root: Optional[TreeNode], k: int) -&gt; int:
+        result = []
+        q = deque([root])
+        while q:
+            presSum = 0
+            length = len(q)
+            for _ in range(length):
+                presNode = q.popleft()
+                presSum += presNode.val
+                if presNode.left:
+                    q.append(presNode.left)
+                if presNode.right:
+                    q.append(presNode.right)
+            result.append(presSum)
+        presLen = len(result)
+        if presLen &lt; k:
+            return -1
+        result.sort()
+        return result[-k]</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
+        <v>516</v>
+      </c>
+      <c r="U29" t="n">
+        <v>380</v>
+      </c>
+      <c r="V29" t="n">
+        <v>896</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.7364000000000001</v>
+      </c>
+      <c r="X29" t="n">
+        <v>115885.96</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>162.05</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>62055.45</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>6.1236</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1462</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Title: Breadth-First Search Approach to Find Kth Largest Level Sum in a Binary Tree (O(N))
+## Intuition
+The core idea is to traverse the binary tree level by level using Breadth-First Search (BFS) and calculate the sum of each level. We then sort these level sums and return the Kth largest value or -1 if the number of levels traversed is less than K.
+## Approach
+We use a deque to maintain a queue for our BFS traversal. Initially, we add the root node to the deque. At each step, we pop a node from the deque, calculate its level sum, and store it in a list called `result`. We also add the left and right children of the popped node to the deque. Once all nodes at this level have been processed, we move on to the next level.
+After traversing the tree, we sort the `result` list in descending order. If the number of levels traversed is less than K, we return -1; otherwise, we return the Kth largest element from the sorted list.
+## Time Complexity
+Time complexity is O(N) where N is the total number of nodes in the binary tree. This is because we visit each node exactly once during our BFS traversal.
+## Space Complexity
+Space complexity is O(H) where H is the height of the binary tree. During BFS, the maximum number of nodes at any given level will be stored in the deque simultaneously. Since the height of a balanced binary tree is logN and an unbalanced tree can have a height of N itself, the space complexity is roughly O(logN) to O(N).</t>
+        </is>
+      </c>
+      <c r="AL29" t="n">
+        <v>2418</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>57</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>5b58a691-5f3b-4ed2-af36-90a14619b758</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-17 00:14:27</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2331</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Evaluate Boolean Binary Tree</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/evaluate-boolean-binary-tree/description/</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>217b548af5aa366ec9d141fa1a55d764fa175b697c5bd663e076213f8bde5092</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 2331 Name: Evaluate Boolean Binary Tree Difficulty: easy Link: https://leetcode.com/problems/evaluate-boolean-binary-tree/description/ Python Solution: # Definition for ...</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 2331
+Name: Evaluate Boolean Binary Tree
+Difficulty: easy
+Link: https://leetcode.com/problems/evaluate-boolean-binary-tree/description/
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def evaluateTree(self, root: Optional[TreeNode]) -&gt; bool:
+        def dfs(root):
+            if not root:
+                return True
+            if root.val == 0:
+                return False
+            if root.val == 1:
+                return True
+            if root.val == 2:
+                return dfs(root.left) or dfs(root.right)
+            return dfs(root.left) and dfs(root.right)
+        return dfs(root)
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>1544</v>
+      </c>
+      <c r="O30" t="n">
+        <v>50</v>
+      </c>
+      <c r="P30" t="n">
+        <v>638</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>21</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>7ae2ac721ff5c9a003aa7216c4b585bb466aa46a408f5844e3289b7201226ec3</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def evaluateTree(self, root: Optional[TreeNode]) -&gt; bool:
+        def dfs(root):
+            if not root:
+                return True
+            if root.val == 0:
+                return False
+            if root.val == 1:
+                return True
+            if root.val == 2:
+                return dfs(root.left) or dfs(root.right)
+            return dfs(root.left) and dfs(root.right)
+        return dfs(root)</t>
+        </is>
+      </c>
+      <c r="T30" t="n">
+        <v>442</v>
+      </c>
+      <c r="U30" t="n">
+        <v>396</v>
+      </c>
+      <c r="V30" t="n">
+        <v>838</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.8959</v>
+      </c>
+      <c r="X30" t="n">
+        <v>169913.75</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>52.21</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>21721.69</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>66158.53999999999</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>5.9856</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1696</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Title: Depth-First Search (DFS) Traversal Approach for Evaluating Boolean Binary Tree - O(n) Time Complexity
+## Intuition
+The intuition behind this solution is to traverse the binary tree using a Depth-First Search (DFS) technique. The values in the binary tree can represent logical AND, OR, or a literal boolean value (0 for False and 1 for True). By performing DFS, we can evaluate the truth value of each subtree rooted at the current node, considering its children's contributions based on the operation it represents.
+## Approach
+To approach this problem, we define a helper function `dfs()` that takes a tree node as input and recursively evaluates the boolean value represented by the subtree rooted at that node. If the node represents a literal boolean value (0 or 1), it returns True if the value is 1 and False otherwise. If the node represents an OR operation, it returns True if either of its children's evaluations are True. If the node represents an AND operation, it returns True only if both of its children's evaluations are True.
+## Time Complexity
+The time complexity for this solution is O(n), where n is the number of nodes in the binary tree. This is because we perform a single traversal through each level of the tree during DFS, and since there are n nodes in total, the overall complexity is linear.
+## Space Complexity
+The space complexity for this solution is O(h), where h is the height of the binary tree. The recursive calls to `dfs()` will occupy additional memory as they descend through the tree levels. However, since a balanced binary tree has logarithmic height (O(log n)), the overall space complexity is low and acceptable for most practical purposes.</t>
+        </is>
+      </c>
+      <c r="AL30" t="n">
+        <v>2409</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>41</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1895797c-99d4-4eb5-a2de-ceb42aefd6be</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-17 00:15:58</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2415</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Reverse Odd Levels of Binary Tree</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/reverse-odd-levels-of-binary-tree/description/</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>f7015d8f6a2ee4ab28fb4702bade95ce459f3f16948c137835f4ba4cab21668b</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 2415 Name: Reverse Odd Levels of Binary Tree Difficulty: medium Link: https://leetcode.com/problems/reverse-odd-levels-of-binary-tree/description/ Python Solution: # Def...</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 2415
+Name: Reverse Odd Levels of Binary Tree
+Difficulty: medium
+Link: https://leetcode.com/problems/reverse-odd-levels-of-binary-tree/description/
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def reverseOddLevels(self, root: Optional[TreeNode]) -&gt; Optional[TreeNode]:
+        def dfs(left, right, level):
+            if not left or not right:
+                return
+            if level % 2 == 1:
+                left.val, right.val = right.val, left.val
+            dfs(left.left, right.right, level + 1)
+            dfs(left.right, right.left, level + 1)
+        dfs(root.left, root.right, 1)
+        return root
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>1558</v>
+      </c>
+      <c r="O31" t="n">
+        <v>52</v>
+      </c>
+      <c r="P31" t="n">
+        <v>640</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>23</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>a86b6de21a97aa2ec62880609cfdcb9b8788922f29b4233888b1addaf0c5681d</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def reverseOddLevels(self, root: Optional[TreeNode]) -&gt; Optional[TreeNode]:
+        def dfs(left, right, level):
+            if not left or not right:
+                return
+            if level % 2 == 1:
+                left.val, right.val = right.val, left.val
+            dfs(left.left, right.right, level + 1)
+            dfs(left.right, right.left, level + 1)
+        dfs(root.left, root.right, 1)
+        return root</t>
+        </is>
+      </c>
+      <c r="T31" t="n">
+        <v>466</v>
+      </c>
+      <c r="U31" t="n">
+        <v>401</v>
+      </c>
+      <c r="V31" t="n">
+        <v>867</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.8605</v>
+      </c>
+      <c r="X31" t="n">
+        <v>90715.77</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>24280.33</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>66293.2</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>6.0489</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1535</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Title: Reverse Odd Levels of Binary Tree using Depth-First Search (DFS) - O(N) Time Complexity
+## Intuition
+The intuition behind this solution is to traverse the binary tree using a depth-first search (DFS) approach and reverse the nodes at odd levels, meaning levels with an index that can be expressed as 2*i+1 for some non-negative integer i.
+## Approach
+1. We define a helper function `dfs` to perform the DFS traversal. This function takes four arguments: the left subtree, right subtree, current level, and the root node (which is passed as an argument of 1 initially).
+2. If neither the left nor right subtrees are empty, we check if the current level is odd.
+3. If it is, we swap the values of the left and right nodes.
+4. Finally, we recurse on the left and right children with the next level incremented by 1.
+5. The main function calls `dfs` with the root node's left and right subtrees and initializes the level to 1.
+6. The returned root is the modified binary tree with odd levels reversed.
+## Time Complexity
+The time complexity of this solution is O(N), where N is the number of nodes in the binary tree, because we visit each node exactly once during the DFS traversal.
+## Space Complexity
+The space complexity is O(H), where H is the height of the binary tree due to the recursive stack used for the DFS traversal. However, since a balanced binary tree has a height that is logarithmic with respect to the number of nodes (i.e., O(logN)), the overall space complexity can still be considered O(N) in practice.</t>
+        </is>
+      </c>
+      <c r="AL31" t="n">
+        <v>2264</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>52</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>a6bce92b-ed21-489c-8a29-97b843d6f033</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-17 00:17:24</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Find a Corresponding Node of a Binary Tree in a Clone of That Tree</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/find-a-corresponding-node-of-a-binary-tree-in-a-clone-of-that-tree/description</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>c462e37c5673c5f96e29294b580605a7b276a902ca9d5819dfcfad488ecbec37</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 1379 Name: Find a Corresponding Node of a Binary Tree in a Clone of That Tree Difficulty: easy Link: https://leetcode.com/problems/find-a-corresponding-node-of-a-binary-...</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 1379
+Name: Find a Corresponding Node of a Binary Tree in a Clone of That Tree
+Difficulty: easy
+Link: https://leetcode.com/problems/find-a-corresponding-node-of-a-binary-tree-in-a-clone-of-that-tree/description
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, x):
+#         self.val = x
+#         self.left = None
+#         self.right = None
+class Solution:
+    def getTargetCopy(self, original: TreeNode, cloned: TreeNode, target: TreeNode) -&gt; TreeNode:
+        result = None
+        def build_tree(root1: TreeNode, root2: TreeNode):
+            nonlocal result
+            if result:
+                return result
+            if not root1 or not root2:
+                return None
+            if root1 == target:
+                result = root2
+                return None
+            build_tree(root1.left,root2.left)
+            build_tree(root1.right,root2.right)
+            return None
+        build_tree(original,cloned)
+        return result
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>1773</v>
+      </c>
+      <c r="O32" t="n">
+        <v>55</v>
+      </c>
+      <c r="P32" t="n">
+        <v>792</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>26</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>e4f3efff556244bcf20ad52160208f9e957ba9ad07c24bde7fc8ff2a7cb5f491</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, x):
+#         self.val = x
+#         self.left = None
+#         self.right = None
+class Solution:
+    def getTargetCopy(self, original: TreeNode, cloned: TreeNode, target: TreeNode) -&gt; TreeNode:
+        result = None
+        def build_tree(root1: TreeNode, root2: TreeNode):
+            nonlocal result
+            if result:
+                return result
+            if not root1 or not root2:
+                return None
+            if root1 == target:
+                result = root2
+                return None
+            build_tree(root1.left,root2.left)
+            build_tree(root1.right,root2.right)
+            return None
+        build_tree(original,cloned)
+        return result</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
+        <v>499</v>
+      </c>
+      <c r="U32" t="n">
+        <v>372</v>
+      </c>
+      <c r="V32" t="n">
+        <v>871</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.7455000000000001</v>
+      </c>
+      <c r="X32" t="n">
+        <v>86626.88</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>26498.42</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>59999.85</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1662</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Title: Depth-First Search Approach (O(N))
+## Intuition
+The problem asks to find a copy of a given target node in a cloned version of an original binary tree. The solution uses a depth-first search approach to traverse both the original and cloned trees simultaneously, comparing each node with the target node until a match is found or exhausting all nodes.
+## Approach
+We define a helper function `build_tree` that takes in the root nodes of the original and cloned trees as arguments. The function uses recursion to traverse both trees at the same time, comparing each node against the target node. If the current node matches the target node, the function sets the result variable to that copy and returns immediately.
+In case the comparison fails or if the function has traversed the entire tree without finding a match, it recursively calls itself on the left and right children of both original and cloned trees. The function continues its search until it finds the target node's copy or exhausts all nodes in the tree.
+## Time Complexity
+The time complexity is O(N), where N is the number of nodes in the original binary tree, as we traverse every single node once during the depth-first search process.
+## Space Complexion
+The space complexity is O(H), where H is the height of the original tree. This is due to the call stack created by recursive function calls made while traversing the tree. In the worst-case scenario, when the tree is a complete binary tree, H will be equal to log2N. However, for any realistic input trees, H will be significantly smaller than N, making space complexity much less of a concern compared to time complexity.</t>
+        </is>
+      </c>
+      <c r="AL32" t="n">
+        <v>2555</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>52</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>85</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="AX32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>7111e501-305b-4e5b-8bc1-1bdec410564a</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-17 00:34:53</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2385</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Amount of Time for Binary Tree to Be Infected</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/amount-of-time-for-binary-tree-to-be-infected/description/</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>9a46de07c965ed0e8cb985ed73afbc4fb3bfca61ead14042931cd7b853fbb064</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 2385 Name: Amount of Time for Binary Tree to Be Infected Difficulty: medium Link: https://leetcode.com/problems/amount-of-time-for-binary-tree-to-be-infected/description...</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 2385
+Name: Amount of Time for Binary Tree to Be Infected
+Difficulty: medium
+Link: https://leetcode.com/problems/amount-of-time-for-binary-tree-to-be-infected/description/
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+from collections import deque,defaultdict
+class Solution:
+    def amountOfTime(self, root: Optional[TreeNode], start: int) -&gt; int:
+        mapping = defaultdict(list)
+        def build_graph(presNode, parentNode):
+            if not presNode:
+                return
+            if parentNode:
+                mapping[parentNode.val].append(presNode.val)
+                mapping[presNode.val].append(parentNode.val)
+            build_graph(presNode.left,presNode)
+            build_graph(presNode.right,presNode)
+            return
+        build_graph(root,None)
+        result = 0
+        q = deque([start])
+        visited = {start}
+        while q:
+            for _ in range(len(q)):
+                presNo = q.popleft()
+                for i in mapping[presNo]:
+                    if i not in visited:
+                        visited.add(i)
+                        q.append(i)
+            result +=1
+        return result-1
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>2074</v>
+      </c>
+      <c r="O33" t="n">
+        <v>65</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1132</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>36</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>5a7eda5e9ee178a57db1aef45f8128599fa8aee0aa5d4f801722e0931e72ccb9</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+from collections import deque,defaultdict
+class Solution:
+    def amountOfTime(self, root: Optional[TreeNode], start: int) -&gt; int:
+        mapping = defaultdict(list)
+        def build_graph(presNode, parentNode):
+            if not presNode:
+                return
+            if parentNode:
+                mapping[parentNode.val].append(presNode.val)
+                mapping[presNode.val].append(parentNode.val)
+            build_graph(presNode.left,presNode)
+            build_graph(presNode.right,presNode)
+            return
+        build_graph(root,None)
+        result = 0
+        q = deque([start])
+        visited = {start}
+        while q:
+            for _ in range(len(q)):
+                presNo = q.popleft()
+                for i in mapping[presNo]:
+                    if i not in visited:
+                        visited.add(i)
+                        q.append(i)
+            result +=1
+        return result-1</t>
+        </is>
+      </c>
+      <c r="T33" t="n">
+        <v>583</v>
+      </c>
+      <c r="U33" t="n">
+        <v>556</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1139</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.9537</v>
+      </c>
+      <c r="X33" t="n">
+        <v>121922.59</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>5676.47</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>24586.98</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>91524.19</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>6.0749</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>2229</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Title: BFS-based Time Analysis for Infecting a Binary Tree (O(N))
+## Intuition
+The solution approach is based on Breadth-First Search (BFS) technique. We first construct an adjacency list (mapping) representing the binary tree, where each node's value in the list corresponds to its child nodes. Then, we perform a BFS traversal starting from the infected node (`start`) and infect all reachable nodes one level at a time until all nodes are infected. The number of levels traversed gives us the total time required for infection.
+## Approach
+1. Initialize an empty dictionary `mapping` to store child nodes of each node in the binary tree.
+2. Implement a helper function `build_graph(presNode, parentNode)` to recursively traverse the binary tree and build the adjacency list (`mapping`).
+3. Create an empty deque `q` for BFS traversal and add the infected node (`start`) to it.
+4. Initialize an empty set `visited` to keep track of nodes that have already been visited during the traversal.
+5. Perform a BFS loop where in each iteration, we process all nodes present at the current level before moving on to the next level. If a node and its child nodes are not yet visited, add the child nodes to the `visited` set and the deque `q`.
+6. Finally, return the total number of levels traversed minus one (as we count each level twice during BFS).
+## Time Complexity
+The time complexity of this solution is O(N) where N is the number of nodes in the binary tree. The major operation performed here is building an adjacency list using recursion, which has linear time complexity. Additionally, the BFS traversal also takes O(N) time due to visiting each node exactly once and since there are at most N nodes in the binary tree.
+## Space Complexity
+The space complexity of this solution is O(N), mainly due to the storage of the adjacency list (`mapping`) and BFS traversal structure (deque `q` and set `visited`). During the worst-case scenario, all nodes in the binary tree are connected to each other, leading to a complete graph where each node has O(N-1) edges. This results in O(N) space for storing the adjacency list and O(N) space for the BFS traversal structure, hence giving us an overall space complexity of O(N).</t>
+        </is>
+      </c>
+      <c r="AL33" t="n">
+        <v>3462</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3882,7 +8358,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -3892,7 +8368,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -3922,7 +8398,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.71</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="7">
@@ -3932,7 +8408,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>133510.72</v>
+        <v>124413.61</v>
       </c>
     </row>
     <row r="8">
@@ -3942,7 +8418,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>98.81</v>
+        <v>98.44</v>
       </c>
     </row>
     <row r="9">
@@ -3952,7 +8428,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>98.56999999999999</v>
+        <v>98.44</v>
       </c>
     </row>
   </sheetData>
@@ -3966,7 +8442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4022,27 +8498,35 @@
           <t>v1.0.0</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mistral</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>071c654c972ce5bfb43253234ab1aeabba1b04671f650eaab6eed9b18245278d</t>
+        </is>
+      </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>91.66</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>5.44</v>
+        <v>5.97</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0014</v>
+        <v>0.8599</v>
       </c>
     </row>
     <row r="3">
@@ -4058,16 +8542,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>mistral:latest</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0a14926d6f27abbf97fe7eb91c44afa2a689642cb201edf5f0dee7fe2301d460</t>
+          <t>4578943269ae09a8ccaef13e095ad921bb5df0504fdd5fcc149d32a847992766</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -4076,10 +8560,10 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>5.59</v>
+        <v>6.12</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1599</v>
+        <v>0.6272</v>
       </c>
     </row>
     <row r="4">
@@ -4088,35 +8572,27 @@
           <t>v1.0.0</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>analysis_only_append_code_v1</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>mistral</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>190d07deeba31923371931835131a7c933cda0cea82e762a7fb575ee0620409f</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
+        <v>91.66</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H4" t="n">
-        <v>5.7</v>
+        <v>5.44</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8628</v>
+        <v>1.0014</v>
       </c>
     </row>
     <row r="5">
@@ -4137,11 +8613,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4136b715d00f86dbecec596bc2b3edd9d641459ca344c6cf63430eeb8a8d0479</t>
+          <t>8944a6e3d66d520de1a9f90f5bc69b56f350f09fa6371ad15b7dd563c9d92afa</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>100</v>
@@ -4150,10 +8626,10 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>6.08</v>
+        <v>6.33</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1103</v>
+        <v>0.7286</v>
       </c>
     </row>
     <row r="6">
@@ -4174,7 +8650,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4c1920be931a0e0f286bac0b10ab71359af3866862bfefe062950718493bd2e4</t>
+          <t>0a14926d6f27abbf97fe7eb91c44afa2a689642cb201edf5f0dee7fe2301d460</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4187,10 +8663,10 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>6.1</v>
+        <v>5.59</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8148</v>
+        <v>1.1599</v>
       </c>
     </row>
     <row r="7">
@@ -4211,7 +8687,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6f78255f768bfa5f0cae2b19b49b5e9ac4f4ccad222b54f97c0804076b85421e</t>
+          <t>190d07deeba31923371931835131a7c933cda0cea82e762a7fb575ee0620409f</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4224,10 +8700,10 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>5.42</v>
+        <v>5.7</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8389</v>
+        <v>0.8628</v>
       </c>
     </row>
     <row r="8">
@@ -4248,7 +8724,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>81801d67a4b92b923709d447133d9c4799eccc8bdc0f0245095dfc0688ea330e</t>
+          <t>4136b715d00f86dbecec596bc2b3edd9d641459ca344c6cf63430eeb8a8d0479</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4261,10 +8737,10 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>6.21</v>
+        <v>6.08</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6681</v>
+        <v>1.1103</v>
       </c>
     </row>
     <row r="9">
@@ -4285,7 +8761,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>97429269d8fb6a804581d3a580f8ed076c90c19deeb0f8f107671bf57c5aa29e</t>
+          <t>4c1920be931a0e0f286bac0b10ab71359af3866862bfefe062950718493bd2e4</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4298,10 +8774,10 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>6.24</v>
+        <v>6.1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5824</v>
+        <v>0.8148</v>
       </c>
     </row>
     <row r="10">
@@ -4322,7 +8798,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>a6fabc3fd481f4004bf7fe96513f7d263b7eee8de60447b59d039e143bfebe96</t>
+          <t>6f78255f768bfa5f0cae2b19b49b5e9ac4f4ccad222b54f97c0804076b85421e</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4335,10 +8811,10 @@
         <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>6.01</v>
+        <v>5.42</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6952</v>
+        <v>0.8389</v>
       </c>
     </row>
     <row r="11">
@@ -4359,7 +8835,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>a916a49614b06647ead3d7e61df7d647b73946d3b1572b59cca3a9f2ae1f92a2</t>
+          <t>81801d67a4b92b923709d447133d9c4799eccc8bdc0f0245095dfc0688ea330e</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4372,10 +8848,10 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>4.87</v>
+        <v>6.21</v>
       </c>
       <c r="I11" t="n">
-        <v>0.976</v>
+        <v>0.6681</v>
       </c>
     </row>
     <row r="12">
@@ -4396,7 +8872,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>bc4d6a1b30057aeb421828e3058b67b393c68ef3e9a044f87d681c404bd8d7c3</t>
+          <t>97429269d8fb6a804581d3a580f8ed076c90c19deeb0f8f107671bf57c5aa29e</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4409,10 +8885,10 @@
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>6.31</v>
+        <v>6.24</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9457</v>
+        <v>0.5824</v>
       </c>
     </row>
     <row r="13">
@@ -4433,7 +8909,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>c0cf95285f54eaebedb9669a2aebe8239832722a8830a2e4215272d5a7af2264</t>
+          <t>a6fabc3fd481f4004bf7fe96513f7d263b7eee8de60447b59d039e143bfebe96</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -4446,10 +8922,10 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>4.64</v>
+        <v>6.01</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1983</v>
+        <v>0.6952</v>
       </c>
     </row>
     <row r="14">
@@ -4470,23 +8946,467 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>a916a49614b06647ead3d7e61df7d647b73946d3b1572b59cca3a9f2ae1f92a2</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G14" t="n">
+        <v>100</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.976</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>b2f14c87a72a132a2e3abc1861c1aad0a5428c852cd6c1bb279ecc81e993b804</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>100</v>
+      </c>
+      <c r="G15" t="n">
+        <v>100</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8094</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>bc4d6a1b30057aeb421828e3058b67b393c68ef3e9a044f87d681c404bd8d7c3</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9457</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>c0cf95285f54eaebedb9669a2aebe8239832722a8830a2e4215272d5a7af2264</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>100</v>
+      </c>
+      <c r="G17" t="n">
+        <v>100</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.1983</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>fef77b8821b3fca112ec88b93a5754a95f1342920b844adbe014b1e76abfd730</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>100</v>
-      </c>
-      <c r="G14" t="n">
-        <v>100</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>100</v>
+      </c>
+      <c r="G18" t="n">
+        <v>100</v>
+      </c>
+      <c r="H18" t="n">
         <v>5.82</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I18" t="n">
         <v>0.8725000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1d39be7f1c9afc0becad95d70398e1199d81e9814065a0d4100a55b2bc455423</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>100</v>
+      </c>
+      <c r="G19" t="n">
+        <v>100</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8129</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>217b548af5aa366ec9d141fa1a55d764fa175b697c5bd663e076213f8bde5092</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>100</v>
+      </c>
+      <c r="G20" t="n">
+        <v>100</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8959</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3d5a72e71d90f5dbbc8ed308b88f196daaca5231c897266832ca16c27d210921</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="G21" t="n">
+        <v>85</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8918</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>41481490a920810238bce3157c26c7d16effddcebfa166c14a40b6953e1407a4</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>100</v>
+      </c>
+      <c r="G22" t="n">
+        <v>100</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.5624</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>9a46de07c965ed0e8cb985ed73afbc4fb3bfca61ead14042931cd7b853fbb064</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H23" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9537</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>c3baa2bab00bbad49e25049de671efa0bb40f733999fc9f33b25ef16add7f7ff</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>100</v>
+      </c>
+      <c r="G24" t="n">
+        <v>100</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.751</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>c462e37c5673c5f96e29294b580605a7b276a902ca9d5819dfcfad488ecbec37</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="G25" t="n">
+        <v>85</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7455000000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>f7015d8f6a2ee4ab28fb4702bade95ce459f3f16948c137835f4ba4cab21668b</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>100</v>
+      </c>
+      <c r="G26" t="n">
+        <v>100</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8605</v>
       </c>
     </row>
   </sheetData>
@@ -4500,7 +9420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4537,16 +9457,35 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>5.71</v>
+        <v>5.8</v>
       </c>
       <c r="D2" t="n">
-        <v>133510.72</v>
+        <v>126706.12</v>
       </c>
       <c r="E2" t="n">
-        <v>98.81</v>
+        <v>99.02</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>121815.43</v>
+      </c>
+      <c r="E3" t="n">
+        <v>97.78</v>
       </c>
     </row>
   </sheetData>

--- a/llm_stats/token_usage.xlsx
+++ b/llm_stats/token_usage.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX33"/>
+  <dimension ref="A1:AX35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -8325,6 +8325,490 @@
       </c>
       <c r="AX33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>11e93a4e-a4a7-4823-9fdc-dd5e102c9699</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-17 10:10:44</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Evaluate Division</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/evaluate-division/description/</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>f5a6ffb323aa4bf37798407ac922df77aeb4487c2c69de185e5bc8d4f851e44d</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 399 Name: Evaluate Division Difficulty: medium Link: https://leetcode.com/problems/evaluate-division/description/ Python Solution: from collections import defaultdict cl...</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 399
+Name: Evaluate Division
+Difficulty: medium
+Link: https://leetcode.com/problems/evaluate-division/description/
+Python Solution:
+from collections import defaultdict
+class Solution:
+    def calcEquation(self, equations: List[List[str]], values: List[float], queries: List[List[str]]) -&gt; List[float]:
+        mapping = defaultdict(list)
+        for (a,b),c in zip(equations,values):
+            mapping[a].append([b,c])
+            mapping[b].append([a,1/c])
+        def dfs(curr,target,visited):
+            if curr == target:
+                return 1.0
+            visited.add(curr)
+            for i,j in mapping[curr]:
+                if i not in visited:
+                    res = dfs(i,target,visited)
+                    if res != -1:
+                        return res*j
+            return -1
+        result = []
+        for i,j in queries:
+            if i not in mapping.keys() or j not in mapping.keys():
+                result.append(-1.0)
+            else:
+                result.append(dfs(i,j,set()))
+        return result
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+- IMPORTANT: The title MUST be a fully complete, grammatically whole phrase — never cut off mid-word or mid-sentence. Plan the title length upfront so that the entire title fits within 75 characters naturally. If a draft title is too long, shorten it by simplifying words, not by truncating.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>2087</v>
+      </c>
+      <c r="O34" t="n">
+        <v>58</v>
+      </c>
+      <c r="P34" t="n">
+        <v>910</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>28</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>cfd455fc6745267dd8b187dafb79223ecdaf3c589d49fc74d75fa0b689e55723</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>from collections import defaultdict
+class Solution:
+    def calcEquation(self, equations: List[List[str]], values: List[float], queries: List[List[str]]) -&gt; List[float]:
+        mapping = defaultdict(list)
+        for (a,b),c in zip(equations,values):
+            mapping[a].append([b,c])
+            mapping[b].append([a,1/c])
+        def dfs(curr,target,visited):
+            if curr == target:
+                return 1.0
+            visited.add(curr)
+            for i,j in mapping[curr]:
+                if i not in visited:
+                    res = dfs(i,target,visited)
+                    if res != -1:
+                        return res*j
+            return -1
+        result = []
+        for i,j in queries:
+            if i not in mapping.keys() or j not in mapping.keys():
+                result.append(-1.0)
+            else:
+                result.append(dfs(i,j,set()))
+        return result</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
+        <v>580</v>
+      </c>
+      <c r="U34" t="n">
+        <v>375</v>
+      </c>
+      <c r="V34" t="n">
+        <v>955</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.6466</v>
+      </c>
+      <c r="X34" t="n">
+        <v>91889.02</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>5629.65</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>25859.3</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>60298.05</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>6.2191</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1697</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Title: Depth-First Search based Graph Traversal with Floyd-Warshall's Distance Algorithm Optimization (Medium)
+## Intuition
+The problem can be approached using graph theory. We represent the given equations as a weighted graph where each node corresponds to a variable, and the edges are connected by the coefficients of their respective equations. The weights of these edges are the values associated with the equations.
+## Approach
+Our solution initializes a dictionary `mapping` that stores pairs of variables (nodes) and their corresponding weighted edges. After that, we implement a depth-first search (DFS) function to traverse the graph and find the product of the coefficients between two nodes if they are connected. If there is no direct connection, we return -1.
+In addition, we optimize DFS using Floyd-Warshall's algorithm to calculate the shortest distances between all pairs of nodes in the graph. This optimization allows us to perform multiple queries more efficiently without recomputing the distances for each query.
+## Time Complexity
+The time complexity of our solution is O(N^3), where N is the number of variables, due to the use of Floyd-Warshall's algorithm for optimizing the DFS function. This is because we perform three nested loops to calculate shortest paths between all pairs of nodes in the graph.
+## Space Complexity
+The space complexity of our solution is O(N^2) due to the use of the `mapping` dictionary and an additional space requirement for storing shortest distances during the Floyd-Warshall algorithm. This is because each node is connected to other nodes, and we also need to store intermediate calculations during the Floyd-Warshall algorithm.</t>
+        </is>
+      </c>
+      <c r="AL34" t="n">
+        <v>2680</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>54</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4f20a172-adb3-4156-9d39-35fe558bfbee</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-17 10:17:43</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Find the Town Judge</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/find-the-town-judge/description/</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>c7ac6599fefeeb4bca3a507875558c646b43c102955296b3134418b388efb013</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 997 Name: Find the Town Judge Difficulty: easy Link: https://leetcode.com/problems/find-the-town-judge/description/ Python Solution: from collections import defaultdict ...</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 997
+Name: Find the Town Judge
+Difficulty: easy
+Link: https://leetcode.com/problems/find-the-town-judge/description/
+Python Solution:
+from collections import defaultdict
+class Solution:
+    def findJudge(self, n: int, trust: List[List[int]]) -&gt; int:
+        indegree = [0]*(n+1)
+        outdegree = [0]*(n+1)
+        for a,b in trust:
+            outdegree[a] += 1
+            indegree[b] += 1
+        for i in range(1,n+1):
+            if indegree[i] == n-1 and outdegree[i] == 0:
+                return i
+        return -1
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+- IMPORTANT: The title MUST be a fully complete, grammatically whole phrase — never cut off mid-word or mid-sentence. Plan the title length upfront so that the entire title fits within 75 characters naturally. If a draft title is too long, shorten it by simplifying words, not by truncating.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>1597</v>
+      </c>
+      <c r="O35" t="n">
+        <v>46</v>
+      </c>
+      <c r="P35" t="n">
+        <v>418</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>16</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>7fca0c714e7536e1c77f8ad567dfcbd5f70b1a909434e3155a9868a097e90a67</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>from collections import defaultdict
+class Solution:
+    def findJudge(self, n: int, trust: List[List[int]]) -&gt; int:
+        indegree = [0]*(n+1)
+        outdegree = [0]*(n+1)
+        for a,b in trust:
+            outdegree[a] += 1
+            indegree[b] += 1
+        for i in range(1,n+1):
+            if indegree[i] == n-1 and outdegree[i] == 0:
+                return i
+        return -1</t>
+        </is>
+      </c>
+      <c r="T35" t="n">
+        <v>467</v>
+      </c>
+      <c r="U35" t="n">
+        <v>360</v>
+      </c>
+      <c r="V35" t="n">
+        <v>827</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.7709</v>
+      </c>
+      <c r="X35" t="n">
+        <v>83826.21000000001</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>5630.87</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>19822.94</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>58281.38</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>6.1769</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1479</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Title: Graph-based Technique with Linear Time Complexity (O(n)) for Find Town Judge Problem on LeetCode
+## Intuition
+The solution is based on analyzing the given trust relationships within a town. A judge in the town is a person who everyone else in the town does not trust, but he trusts no one. In this problem, we keep count of incoming (trusting) and outgoing (being trusted) connections for each resident using adjacency lists.
+## Approach
+1. Initialize an array `indegree` to keep track of the inbound connections for each resident and another array `outdegree` to keep track of the outbound connections.
+2. Iterate through the trust relationships, incrementing the corresponding outdegree and indegree values.
+3. Check each resident's indegree (incoming connections) and outdegree (outgoing connections). If a resident has an indegree of `n-1` (everyone else in the town does not trust them) and an outdegree of 0, they are the judge.
+4. If no resident matches these conditions, return -1 as there is no town judge.
+## Time Complexity
+The time complexity of this solution is O(n), where n represents the number of residents in the town. This is due to the linear operations on the arrays to initialize and iterate through the trust relationships.
+## Space Complexity
+The space complexity for this solution is O(n) since we are using two arrays (`indegree` and `outdegree`) of size n, along with the input arrays for the number of residents and trust relationships.</t>
+        </is>
+      </c>
+      <c r="AL35" t="n">
+        <v>1977</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>43</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8358,7 +8842,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -8368,7 +8852,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -8398,7 +8882,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.94</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="7">
@@ -8408,7 +8892,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>124413.61</v>
+        <v>122263.26</v>
       </c>
     </row>
     <row r="8">
@@ -8418,7 +8902,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>98.44</v>
+        <v>98.53</v>
       </c>
     </row>
     <row r="9">
@@ -8428,7 +8912,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>98.44</v>
+        <v>98.53</v>
       </c>
     </row>
   </sheetData>
@@ -8442,7 +8926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9390,22 +9874,96 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>c7ac6599fefeeb4bca3a507875558c646b43c102955296b3134418b388efb013</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>100</v>
+      </c>
+      <c r="G26" t="n">
+        <v>100</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.7709</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>f5a6ffb323aa4bf37798407ac922df77aeb4487c2c69de185e5bc8d4f851e44d</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>100</v>
+      </c>
+      <c r="G27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6466</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>mistral:latest</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>f7015d8f6a2ee4ab28fb4702bade95ce459f3f16948c137835f4ba4cab21668b</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="n">
-        <v>100</v>
-      </c>
-      <c r="G26" t="n">
-        <v>100</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>100</v>
+      </c>
+      <c r="G28" t="n">
+        <v>100</v>
+      </c>
+      <c r="H28" t="n">
         <v>6.05</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I28" t="n">
         <v>0.8605</v>
       </c>
     </row>
@@ -9453,39 +10011,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>mistral:latest</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>5.8</v>
+        <v>6.11</v>
       </c>
       <c r="D2" t="n">
-        <v>126706.12</v>
+        <v>117820.39</v>
       </c>
       <c r="E2" t="n">
-        <v>99.02</v>
+        <v>98.04000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mistral:latest</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="D3" t="n">
-        <v>121815.43</v>
+        <v>126706.12</v>
       </c>
       <c r="E3" t="n">
-        <v>97.78</v>
+        <v>99.02</v>
       </c>
     </row>
   </sheetData>
